--- a/docs/script_to_output_manifest.xlsx
+++ b/docs/script_to_output_manifest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mzx/Desktop/sGSVA/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{3CBD9FEE-EA4D-B24B-AE5F-E625A8FA12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{923D23C8-6C4D-49D0-BBB3-EE149C3F3BC0}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{3CBD9FEE-EA4D-B24B-AE5F-E625A8FA12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE429509-21DC-43CE-BFD9-2CCFE71DBDD6}"/>
   <bookViews>
     <workbookView xWindow="7620" yWindow="500" windowWidth="21180" windowHeight="16940" xr2:uid="{3CCF5D24-2254-1D48-97DC-E334113CC7EA}"/>
   </bookViews>
@@ -131,7 +131,7 @@
     <t>results/figures/Fig5_DLPFC_main.pdf</t>
   </si>
   <si>
-    <t>Laminar pathway architecture, cross-section meta-analysis</t>
+    <t>Laminar pathway architecture, cross-section recurrence</t>
   </si>
   <si>
     <t>Fig. 6</t>

--- a/docs/script_to_output_manifest.xlsx
+++ b/docs/script_to_output_manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mzx/Desktop/sGSVA/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{3CBD9FEE-EA4D-B24B-AE5F-E625A8FA12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE429509-21DC-43CE-BFD9-2CCFE71DBDD6}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{3CBD9FEE-EA4D-B24B-AE5F-E625A8FA12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152A8C26-6671-4C23-8964-CD204B625FC9}"/>
   <bookViews>
     <workbookView xWindow="7620" yWindow="500" windowWidth="21180" windowHeight="16940" xr2:uid="{3CCF5D24-2254-1D48-97DC-E334113CC7EA}"/>
   </bookViews>
@@ -110,7 +110,7 @@
     <t>Results, Breast Visium</t>
   </si>
   <si>
-    <t>scripts/BreastVisium/breast_figures.R</t>
+    <t>scripts/BreastVisium/breast_visium_figures.R</t>
   </si>
   <si>
     <t>results/figures/Fig4_BreastVisium_main.pdf</t>
@@ -242,7 +242,7 @@
     <t>Table 2</t>
   </si>
   <si>
-    <t>scripts/BreastVisium/breast_tables.R</t>
+    <t>scripts/BreastVisium/breast_visium_tables.R</t>
   </si>
   <si>
     <t>results/tables/main_table2_breast_moran_geary_summary.csv</t>
@@ -368,7 +368,7 @@
     <t>Supplement Data 1</t>
   </si>
   <si>
-    <t>scripts/Simulation/simulation_analysis.R</t>
+    <t>scripts/Simulation/simulation_with_gsdensity.R</t>
   </si>
   <si>
     <t>results/supplementary_data/Supplement Data 1.xlsx</t>
@@ -392,7 +392,7 @@
     <t>Supplement Data 3</t>
   </si>
   <si>
-    <t>scripts/BreastVisium/breast_analysis.R</t>
+    <t>scripts/BreastVisium/breast_visium_with_gsdensity.R, scripts/BreastVisium/breast_visium_evaluate_enrichmap.R</t>
   </si>
   <si>
     <t>results/supplementary_data/Supplement Data 3.xlsx</t>
@@ -1426,7 +1426,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="32.25">
+    <row r="32" spans="1:6" ht="81">
       <c r="A32" s="4" t="s">
         <v>117</v>
       </c>

--- a/docs/script_to_output_manifest.xlsx
+++ b/docs/script_to_output_manifest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mzx/Desktop/sGSVA/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{3CBD9FEE-EA4D-B24B-AE5F-E625A8FA12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152A8C26-6671-4C23-8964-CD204B625FC9}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{3CBD9FEE-EA4D-B24B-AE5F-E625A8FA12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FBA8714-3EF5-4498-AFB0-A42991B68AC9}"/>
   <bookViews>
     <workbookView xWindow="7620" yWindow="500" windowWidth="21180" windowHeight="16940" xr2:uid="{3CCF5D24-2254-1D48-97DC-E334113CC7EA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="137">
   <si>
     <t>Output ID</t>
   </si>
@@ -65,13 +65,13 @@
     <t>Results, Overview</t>
   </si>
   <si>
-    <t>Manually created schematic</t>
-  </si>
-  <si>
-    <t>results/figures/Fig1_illustration.png</t>
-  </si>
-  <si>
-    <t>Overview of sGSVA workflow</t>
+    <t>Manually created; no generating script</t>
+  </si>
+  <si>
+    <t>No output file</t>
+  </si>
+  <si>
+    <t>Overview workflow</t>
   </si>
   <si>
     <t>Fig. 2</t>
@@ -86,7 +86,7 @@
     <t>results/figures/Fig2_simulation_performance.pdf</t>
   </si>
   <si>
-    <t>Simulation AUROC, Spearman, data-driven sGSVA retention</t>
+    <t>Simulation AUROC, Spearman, data-driven SpaRGS retention</t>
   </si>
   <si>
     <t>Fig. 3</t>
@@ -218,6 +218,9 @@
     <t>Supplementary Fig. S8</t>
   </si>
   <si>
+    <t>scripts/Xenium/Xenium_analysis.R</t>
+  </si>
+  <si>
     <t>results/figures/supplement_Fig_S8_Xenium_preprocessing.pdf</t>
   </si>
   <si>
@@ -233,7 +236,7 @@
     <t>scripts/Simulation/simulation_tables.R</t>
   </si>
   <si>
-    <t>results/tables/main_table1_simulation_retained_matched_summary.xlsx</t>
+    <t>results/tables/main_table1_simulation_retained_matched_summary.csv</t>
   </si>
   <si>
     <t>AUROC, spearman and runtime across scenarios</t>
@@ -263,10 +266,10 @@
     <t>Supplementary Table S3A-C</t>
   </si>
   <si>
-    <t>results/tables/supplement_Table_S3A_simulation_sgsva_retention_by_signal.csv, supplement_Table_S3B_simulation_sgsva_retained_vs_nonretained.csv, supplement_Table_S3C_simulation_signed_orientation_summary.csv</t>
-  </si>
-  <si>
-    <t>Simulation retention, retained-case characteristics, signed orientation for data-driven sGSVA</t>
+    <t>results/tables/supplement_Table_S3A_simulation_spargs_retention_by_signal.csv, supplement_Table_S3B_simulation_spargs_retained_vs_nonretained.csv, supplement_Table_S3C_simulation_signed_orientation_summary.csv</t>
+  </si>
+  <si>
+    <t>Simulation retention, retained-case characteristics, signed orientation for data-driven SpaRGS</t>
   </si>
   <si>
     <t>Supplement Table S4</t>
@@ -311,10 +314,10 @@
     <t>Supplement Table S8</t>
   </si>
   <si>
-    <t>results/tables/supplement_Table_S8_breast_sgsva_orientation_diagnostics.csv</t>
-  </si>
-  <si>
-    <t>sGSVA orientaion diagnostics</t>
+    <t>results/tables/supplement_Table_S8_breast_spargs_orientation_diagnostics.csv</t>
+  </si>
+  <si>
+    <t>SpaRGS orientaion diagnostics</t>
   </si>
   <si>
     <t>Supplement Table S9</t>
@@ -347,7 +350,7 @@
     <t>Supplement Table S12A-B</t>
   </si>
   <si>
-    <t>scripts/Xenium/xenium_tables.R</t>
+    <t>scripts/Xenium/Xenium_tables.R</t>
   </si>
   <si>
     <t>results/tables/supplement_Table_S12A_xenium_median_autocorrelation_summary.csv, supplement_Table_S12B_xenium_paired_moran_geary_bootstrap.csv</t>
@@ -359,19 +362,43 @@
     <t>Supplement Table S13A-B</t>
   </si>
   <si>
-    <t>results/tables/supplementary_Table_S13_xenium_gene_overlap_and_nonoverlap_correlation.csv</t>
+    <t>results/tables/supplement_Table_S13_xenium_gene_overlap_and_nonoverlap_correlation.csv</t>
   </si>
   <si>
     <t>Pathway-module gene overlap and non-overlap concordance sensitivity</t>
   </si>
   <si>
+    <t>Supplement Table S14</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Biological interpretation and supporting evidence</t>
+  </si>
+  <si>
+    <t>Supplement Table S15</t>
+  </si>
+  <si>
+    <t>Spatial randomization testing runtime</t>
+  </si>
+  <si>
+    <t>Supplement Table S16</t>
+  </si>
+  <si>
+    <t>Data availability</t>
+  </si>
+  <si>
+    <t>public datasets and accesss information</t>
+  </si>
+  <si>
     <t>Supplement Data 1</t>
   </si>
   <si>
     <t>scripts/Simulation/simulation_with_gsdensity.R</t>
   </si>
   <si>
-    <t>results/supplementary_data/Supplement Data 1.xlsx</t>
+    <t>results/supplementary_data/Supplementary Data 1.xlsx</t>
   </si>
   <si>
     <t>Full simulation performance analysis results</t>
@@ -380,10 +407,10 @@
     <t>Supplement Data 2</t>
   </si>
   <si>
-    <t>scripts/Robustness/robutness_analysis.R</t>
-  </si>
-  <si>
-    <t>results/supplementary_data/Supplement Data 2.xlsx</t>
+    <t>scripts/Robustness/robustness_analysis.R</t>
+  </si>
+  <si>
+    <t>results/supplementary_data/Supplementary Data 2.xlsx</t>
   </si>
   <si>
     <t>Full robustness and sensitivity analysis results</t>
@@ -395,7 +422,7 @@
     <t>scripts/BreastVisium/breast_visium_with_gsdensity.R, scripts/BreastVisium/breast_visium_evaluate_enrichmap.R</t>
   </si>
   <si>
-    <t>results/supplementary_data/Supplement Data 3.xlsx</t>
+    <t>results/supplementary_data/Supplementary Data 3.xlsx</t>
   </si>
   <si>
     <t>Full breast Visium analysis results</t>
@@ -407,7 +434,7 @@
     <t>scripts/DLPFC/DLPFC_analysis.R</t>
   </si>
   <si>
-    <t>results/supplementary_data/Supplement Data 4.xlsx</t>
+    <t>results/supplementary_data/Supplementary Data 4.xlsx</t>
   </si>
   <si>
     <t>Full DLPFC analysis results</t>
@@ -416,10 +443,7 @@
     <t>Supplement Data 5</t>
   </si>
   <si>
-    <t>scripts/Xenium/Xenium_analysis.R</t>
-  </si>
-  <si>
-    <t>results/supplementary_data/Supplement Data 5.xlsx</t>
+    <t>results/supplementary_data/Supplementary Data 5.xlsx</t>
   </si>
   <si>
     <t>Full Xenium FFPE analysis results</t>
@@ -429,7 +453,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -452,6 +476,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -473,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -481,6 +511,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -797,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED98093B-BA47-4749-9E42-166AE67C5504}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="3" max="3" width="18.625" customWidth="1"/>
@@ -826,23 +860,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" ht="28.5" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1097,58 +1131,58 @@
         <v>33</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="48.75">
       <c r="A16" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="32.1" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>38</v>
@@ -1157,18 +1191,18 @@
         <v>13</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="36.950000000000003" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
@@ -1177,18 +1211,18 @@
         <v>13</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="48.75">
       <c r="A20" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>38</v>
@@ -1197,18 +1231,18 @@
         <v>13</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="48.75">
       <c r="A21" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>38</v>
@@ -1217,18 +1251,18 @@
         <v>13</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="33" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>38</v>
@@ -1237,18 +1271,18 @@
         <v>18</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="48.75">
       <c r="A23" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>38</v>
@@ -1257,18 +1291,18 @@
         <v>23</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="48.75">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>38</v>
@@ -1277,18 +1311,18 @@
         <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="48.75">
       <c r="A25" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>38</v>
@@ -1297,18 +1331,18 @@
         <v>23</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="48.75">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>38</v>
@@ -1317,18 +1351,18 @@
         <v>23</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="48.75">
       <c r="A27" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>38</v>
@@ -1337,18 +1371,18 @@
         <v>23</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="81">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
@@ -1357,18 +1391,18 @@
         <v>33</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="64.5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="48.75">
       <c r="A29" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>38</v>
@@ -1377,30 +1411,30 @@
         <v>33</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="32.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>13</v>
+      <c r="C30" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>112</v>
@@ -1413,79 +1447,142 @@
       <c r="B31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>18</v>
+      <c r="C31" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E31" s="4" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="32.25">
+      <c r="A32" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="B32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="81">
-      <c r="A32" s="4" t="s">
+      <c r="D32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="32.25">
       <c r="A33" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="32.25">
       <c r="A34" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="3" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="81">
+      <c r="A35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="32.25">
+      <c r="A36" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="32.25">
+      <c r="A37" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
+      <c r="D37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75"/>
+    <row r="39" spans="1:6" ht="15.75"/>
+    <row r="40" spans="1:6" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
